--- a/CorrectionExemplesHAS/ig/StructureDefinition-fr-mp-substance.xlsx
+++ b/CorrectionExemplesHAS/ig/StructureDefinition-fr-mp-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:32:00+00:00</t>
+    <t>2025-11-07T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CorrectionExemplesHAS/ig/StructureDefinition-fr-mp-substance.xlsx
+++ b/CorrectionExemplesHAS/ig/StructureDefinition-fr-mp-substance.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Meditinal Product Substance</t>
+    <t>FR Medicinal Product Substance</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:34:21+00:00</t>
+    <t>2025-11-07T09:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
